--- a/data/country_baselines/Updated/Baseline information_Mozambique_06.05.26.xlsx
+++ b/data/country_baselines/Updated/Baseline information_Mozambique_06.05.26.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10302"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Oryn\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2ae90f5cbd0fd171/AMC/HIV Prioritization tool/HIV_prioritization_tool/data/country_baselines/Updated/"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A0AB2E9-CBC4-4949-AF91-C5F0F6D11BA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{4C7C335E-1002-674F-9F40-BA0DD4A4E57A}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="15820" xr2:uid="{4C7C335E-1002-674F-9F40-BA0DD4A4E57A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029" calcOnSave="0"/>
+  <calcPr calcId="191029" calcCompleted="0"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -214,8 +214,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="165" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="164" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -366,7 +366,7 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="20">
@@ -379,7 +379,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="9" xfId="2" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -407,14 +410,11 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="9" xfId="2" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Percent" xfId="2" builtinId="5"/>
+    <cellStyle name="Per cent" xfId="2" builtinId="5"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -747,14 +747,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1FAF0563-D6D0-C349-AAA5-E02739123A65}">
   <dimension ref="A1:J39"/>
-  <sheetFormatPr defaultColWidth="10.6640625" defaultRowHeight="16" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="69.9140625" customWidth="1"/>
+    <col min="1" max="1" width="69.83203125" customWidth="1"/>
     <col min="2" max="2" width="16.5" bestFit="1" customWidth="1"/>
     <col min="3" max="4" width="22.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="48" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:10" ht="51" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>27</v>
       </c>
@@ -768,7 +768,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>31</v>
       </c>
@@ -776,7 +776,7 @@
       <c r="C2" s="2"/>
       <c r="D2" s="1"/>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
@@ -790,7 +790,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>1</v>
       </c>
@@ -802,7 +802,7 @@
       </c>
       <c r="D4" s="1"/>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>2</v>
       </c>
@@ -816,7 +816,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
         <v>3</v>
       </c>
@@ -830,7 +830,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
         <v>4</v>
       </c>
@@ -842,7 +842,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="8" spans="1:10" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:10" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>5</v>
       </c>
@@ -856,14 +856,14 @@
         <v>39</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="H9" s="8" t="s">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="H9" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="I9" s="9"/>
-      <c r="J9" s="10"/>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="I9" s="12"/>
+      <c r="J9" s="13"/>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>6</v>
       </c>
@@ -876,22 +876,22 @@
       <c r="D10" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="H10" s="11"/>
-      <c r="I10" s="12"/>
-      <c r="J10" s="13"/>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="H10" s="14"/>
+      <c r="I10" s="15"/>
+      <c r="J10" s="16"/>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
         <v>10</v>
       </c>
       <c r="B11" s="2"/>
       <c r="C11" s="2"/>
       <c r="D11" s="1"/>
-      <c r="H11" s="11"/>
-      <c r="I11" s="12"/>
-      <c r="J11" s="13"/>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="H11" s="14"/>
+      <c r="I11" s="15"/>
+      <c r="J11" s="16"/>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
         <v>9</v>
       </c>
@@ -904,11 +904,11 @@
       <c r="D12" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="H12" s="11"/>
-      <c r="I12" s="12"/>
-      <c r="J12" s="13"/>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="H12" s="14"/>
+      <c r="I12" s="15"/>
+      <c r="J12" s="16"/>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
         <v>8</v>
       </c>
@@ -921,11 +921,11 @@
       <c r="D13" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="H13" s="11"/>
-      <c r="I13" s="12"/>
-      <c r="J13" s="13"/>
-    </row>
-    <row r="14" spans="1:10" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="H13" s="14"/>
+      <c r="I13" s="15"/>
+      <c r="J13" s="16"/>
+    </row>
+    <row r="14" spans="1:10" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>7</v>
       </c>
@@ -938,11 +938,11 @@
       <c r="D14" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="H14" s="14"/>
-      <c r="I14" s="15"/>
-      <c r="J14" s="16"/>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="H14" s="17"/>
+      <c r="I14" s="18"/>
+      <c r="J14" s="19"/>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
         <v>11</v>
       </c>
@@ -957,7 +957,7 @@
       </c>
       <c r="F15" s="4"/>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
         <v>12</v>
       </c>
@@ -971,10 +971,10 @@
         <v>40</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
       <c r="B17" s="4"/>
     </row>
-    <row r="18" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
         <v>22</v>
       </c>
@@ -982,7 +982,7 @@
       <c r="C18" s="1"/>
       <c r="D18" s="1"/>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
         <v>20</v>
       </c>
@@ -996,7 +996,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
         <v>19</v>
       </c>
@@ -1010,21 +1010,21 @@
         <v>43</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
         <v>18</v>
       </c>
       <c r="B21" s="3">
         <v>0</v>
       </c>
-      <c r="C21" s="17">
+      <c r="C21" s="8">
         <v>1E-3</v>
       </c>
       <c r="D21" s="1" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1038,14 +1038,14 @@
         <v>45</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
         <v>21</v>
       </c>
       <c r="B23" s="3">
         <v>0.05</v>
       </c>
-      <c r="C23" s="18">
+      <c r="C23" s="9">
         <f>(0.4+0.1+0.1+1.1)/100</f>
         <v>1.7000000000000001E-2</v>
       </c>
@@ -1053,10 +1053,10 @@
         <v>44</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
       <c r="B24" s="5"/>
     </row>
-    <row r="25" spans="1:4" ht="17" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:4" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
         <v>16</v>
       </c>
@@ -1070,7 +1070,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="26" spans="1:4" ht="17" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:4" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="1" t="s">
         <v>25</v>
       </c>
@@ -1084,7 +1084,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="27" spans="1:4" ht="17" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:4" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="1" t="s">
         <v>26</v>
       </c>
@@ -1092,12 +1092,12 @@
         <v>0.8</v>
       </c>
       <c r="C27" s="1"/>
-      <c r="D27" s="19" t="s">
+      <c r="D27" s="10" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="28" spans="1:4" ht="17" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:4" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A29" s="1" t="s">
         <v>28</v>
       </c>
@@ -1111,7 +1111,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A30" s="1" t="s">
         <v>29</v>
       </c>
@@ -1125,10 +1125,10 @@
         <v>50</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.2">
       <c r="B31" s="4"/>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A32" s="1" t="s">
         <v>13</v>
       </c>
@@ -1142,7 +1142,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A33" s="1" t="s">
         <v>14</v>
       </c>
@@ -1156,7 +1156,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A34" s="1" t="s">
         <v>15</v>
       </c>
@@ -1168,7 +1168,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A35" s="1" t="s">
         <v>23</v>
       </c>
@@ -1182,7 +1182,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A36" s="1" t="s">
         <v>24</v>
       </c>
@@ -1196,10 +1196,10 @@
         <v>54</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.2">
       <c r="B37" s="5"/>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.2">
       <c r="C39">
         <v>1280837</v>
       </c>

--- a/data/country_baselines/Updated/Baseline information_Mozambique_06.05.26.xlsx
+++ b/data/country_baselines/Updated/Baseline information_Mozambique_06.05.26.xlsx
@@ -15,7 +15,7 @@
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029" calcCompleted="0"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>

--- a/data/country_baselines/Updated/Baseline information_Mozambique_06.05.26.xlsx
+++ b/data/country_baselines/Updated/Baseline information_Mozambique_06.05.26.xlsx
@@ -15,7 +15,7 @@
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" calcCompleted="0"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>

--- a/data/country_baselines/Updated/Baseline information_Mozambique_06.05.26.xlsx
+++ b/data/country_baselines/Updated/Baseline information_Mozambique_06.05.26.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2ae90f5cbd0fd171/AMC/HIV Prioritization tool/HIV_prioritization_tool/data/country_baselines/Updated/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A0AB2E9-CBC4-4949-AF91-C5F0F6D11BA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{2A0AB2E9-CBC4-4949-AF91-C5F0F6D11BA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{06C4556E-71E2-114D-9569-DD335E4E3E2B}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="15820" xr2:uid="{4C7C335E-1002-674F-9F40-BA0DD4A4E57A}"/>
   </bookViews>
@@ -887,6 +887,10 @@
       <c r="B11" s="2"/>
       <c r="C11" s="2"/>
       <c r="D11" s="1"/>
+      <c r="E11" s="4">
+        <f>C10-C12-C14</f>
+        <v>11237387</v>
+      </c>
       <c r="H11" s="14"/>
       <c r="I11" s="15"/>
       <c r="J11" s="16"/>

--- a/data/country_baselines/Updated/Baseline information_Mozambique_06.05.26.xlsx
+++ b/data/country_baselines/Updated/Baseline information_Mozambique_06.05.26.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{2A0AB2E9-CBC4-4949-AF91-C5F0F6D11BA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{06C4556E-71E2-114D-9569-DD335E4E3E2B}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="15820" xr2:uid="{4C7C335E-1002-674F-9F40-BA0DD4A4E57A}"/>
+    <workbookView xWindow="1440" yWindow="-18400" windowWidth="28800" windowHeight="15820" xr2:uid="{4C7C335E-1002-674F-9F40-BA0DD4A4E57A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>

--- a/data/country_baselines/Updated/Baseline information_Mozambique_06.05.26.xlsx
+++ b/data/country_baselines/Updated/Baseline information_Mozambique_06.05.26.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{2A0AB2E9-CBC4-4949-AF91-C5F0F6D11BA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{06C4556E-71E2-114D-9569-DD335E4E3E2B}"/>
   <bookViews>
-    <workbookView xWindow="1440" yWindow="-18400" windowWidth="28800" windowHeight="15820" xr2:uid="{4C7C335E-1002-674F-9F40-BA0DD4A4E57A}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="15900" xr2:uid="{4C7C335E-1002-674F-9F40-BA0DD4A4E57A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>

--- a/data/country_baselines/Updated/Baseline information_Mozambique_06.05.26.xlsx
+++ b/data/country_baselines/Updated/Baseline information_Mozambique_06.05.26.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{2A0AB2E9-CBC4-4949-AF91-C5F0F6D11BA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{06C4556E-71E2-114D-9569-DD335E4E3E2B}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="15900" xr2:uid="{4C7C335E-1002-674F-9F40-BA0DD4A4E57A}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="15820" xr2:uid="{4C7C335E-1002-674F-9F40-BA0DD4A4E57A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
